--- a/diseases/d229/2026-2029.xlsx
+++ b/diseases/d229/2026-2029.xlsx
@@ -8673,6 +8673,405 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>D229</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>multidrug-resistant-pseudomonas-aeruginosa-infection</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Multidrug-resistant Pseudomonas aeruginosa infection</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>D229</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Multidrug-resistant Pseudomonas aeruginosa infection</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>多重耐药铜绿假单胞菌感染</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>2</v>
+      </c>
+      <c r="O42" t="n">
+        <v>2</v>
+      </c>
+      <c r="P42" t="n">
+        <v>2</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0.001633616815131532</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>SER_JP_MDR_PSEUDOMONAS_AERUGINOSA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP42" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ42" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS42" t="inlineStr">
+        <is>
+          <t>SER_JP_MDR_PSEUDOMONAS_AERUGINOSA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV42" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA42" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB42" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC42" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>D229</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>multidrug-resistant-pseudomonas-aeruginosa-infection</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Multidrug-resistant Pseudomonas aeruginosa infection</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>D229</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Multidrug-resistant Pseudomonas aeruginosa infection</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>多重耐药铜绿假单胞菌感染</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>2</v>
+      </c>
+      <c r="O43" t="n">
+        <v>2</v>
+      </c>
+      <c r="P43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>SER_JP_MDR_PSEUDOMONAS_AERUGINOSA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>SER_JP_MDR_PSEUDOMONAS_AERUGINOSA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Multidrug-resistant Pseudomonas aeruginosa infection</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG43" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Japan NIID multidrug-resistant Pseudomonas aeruginosa infection notifications.</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN43" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP43" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ43" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS43" t="inlineStr">
+        <is>
+          <t>SER_JP_MDR_PSEUDOMONAS_AERUGINOSA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV43" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA43" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB43" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC43" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8706,7 +9105,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -8789,7 +9188,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10">
@@ -8799,7 +9198,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11">
@@ -8819,7 +9218,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13">
@@ -8851,7 +9250,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d229/2026-2029.xlsx
+++ b/diseases/d229/2026-2029.xlsx
@@ -9072,6 +9072,405 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>D229</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>multidrug-resistant-pseudomonas-aeruginosa-infection</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Multidrug-resistant Pseudomonas aeruginosa infection</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>D229</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Multidrug-resistant Pseudomonas aeruginosa infection</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>多重耐药铜绿假单胞菌感染</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N44" t="n">
+        <v>2</v>
+      </c>
+      <c r="O44" t="n">
+        <v>2</v>
+      </c>
+      <c r="P44" t="n">
+        <v>2</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0.001633616815131532</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>SER_JP_MDR_PSEUDOMONAS_AERUGINOSA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP44" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ44" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS44" t="inlineStr">
+        <is>
+          <t>SER_JP_MDR_PSEUDOMONAS_AERUGINOSA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV44" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA44" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB44" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC44" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>D229</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>multidrug-resistant-pseudomonas-aeruginosa-infection</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Multidrug-resistant Pseudomonas aeruginosa infection</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>D229</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Multidrug-resistant Pseudomonas aeruginosa infection</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>多重耐药铜绿假单胞菌感染</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>2</v>
+      </c>
+      <c r="O45" t="n">
+        <v>2</v>
+      </c>
+      <c r="P45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>SER_JP_MDR_PSEUDOMONAS_AERUGINOSA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>SER_JP_MDR_PSEUDOMONAS_AERUGINOSA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Multidrug-resistant Pseudomonas aeruginosa infection</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Japan NIID multidrug-resistant Pseudomonas aeruginosa infection notifications.</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN45" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP45" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ45" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS45" t="inlineStr">
+        <is>
+          <t>SER_JP_MDR_PSEUDOMONAS_AERUGINOSA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV45" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA45" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB45" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC45" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9105,7 +9504,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -9188,7 +9587,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10">
@@ -9198,7 +9597,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11">
@@ -9218,7 +9617,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
@@ -9250,7 +9649,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d229/2026-2029.xlsx
+++ b/diseases/d229/2026-2029.xlsx
@@ -1007,7 +1007,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6593,7 +6593,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6992,7 +6992,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7790,7 +7790,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8189,7 +8189,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8588,7 +8588,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8987,7 +8987,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9466,6 +9466,405 @@
         </is>
       </c>
       <c r="BC45" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>D229</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>multidrug-resistant-pseudomonas-aeruginosa-infection</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Multidrug-resistant Pseudomonas aeruginosa infection</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>D229</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Multidrug-resistant Pseudomonas aeruginosa infection</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>多重耐药铜绿假单胞菌感染</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>3</v>
+      </c>
+      <c r="O46" t="n">
+        <v>3</v>
+      </c>
+      <c r="P46" t="n">
+        <v>3</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0.002450425222697299</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>SER_JP_MDR_PSEUDOMONAS_AERUGINOSA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP46" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ46" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS46" t="inlineStr">
+        <is>
+          <t>SER_JP_MDR_PSEUDOMONAS_AERUGINOSA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV46" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA46" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB46" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC46" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>D229</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>multidrug-resistant-pseudomonas-aeruginosa-infection</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Multidrug-resistant Pseudomonas aeruginosa infection</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>D229</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Multidrug-resistant Pseudomonas aeruginosa infection</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>多重耐药铜绿假单胞菌感染</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>3</v>
+      </c>
+      <c r="O47" t="n">
+        <v>3</v>
+      </c>
+      <c r="P47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>SER_JP_MDR_PSEUDOMONAS_AERUGINOSA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>SER_JP_MDR_PSEUDOMONAS_AERUGINOSA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Multidrug-resistant Pseudomonas aeruginosa infection</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG47" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Japan NIID multidrug-resistant Pseudomonas aeruginosa infection notifications.</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN47" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP47" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ47" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS47" t="inlineStr">
+        <is>
+          <t>SER_JP_MDR_PSEUDOMONAS_AERUGINOSA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV47" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA47" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB47" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC47" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -9504,7 +9903,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -9587,7 +9986,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10">
@@ -9597,7 +9996,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11">
@@ -9617,7 +10016,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
@@ -9649,7 +10048,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d229/2026-2029.xlsx
+++ b/diseases/d229/2026-2029.xlsx
@@ -9870,6 +9870,405 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>D229</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>multidrug-resistant-pseudomonas-aeruginosa-infection</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Multidrug-resistant Pseudomonas aeruginosa infection</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>D229</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Multidrug-resistant Pseudomonas aeruginosa infection</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>多重耐药铜绿假单胞菌感染</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>6</v>
+      </c>
+      <c r="O48" t="n">
+        <v>6</v>
+      </c>
+      <c r="P48" t="n">
+        <v>6</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0.004900850445394598</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>SER_JP_MDR_PSEUDOMONAS_AERUGINOSA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP48" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ48" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS48" t="inlineStr">
+        <is>
+          <t>SER_JP_MDR_PSEUDOMONAS_AERUGINOSA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV48" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA48" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB48" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC48" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>D229</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>multidrug-resistant-pseudomonas-aeruginosa-infection</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Multidrug-resistant Pseudomonas aeruginosa infection</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>D229</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Multidrug-resistant Pseudomonas aeruginosa infection</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>多重耐药铜绿假单胞菌感染</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>6</v>
+      </c>
+      <c r="O49" t="n">
+        <v>6</v>
+      </c>
+      <c r="P49" t="n">
+        <v>6</v>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>SER_JP_MDR_PSEUDOMONAS_AERUGINOSA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>SER_JP_MDR_PSEUDOMONAS_AERUGINOSA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Multidrug-resistant Pseudomonas aeruginosa infection</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD49" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG49" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Japan NIID multidrug-resistant Pseudomonas aeruginosa infection notifications.</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN49" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP49" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ49" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS49" t="inlineStr">
+        <is>
+          <t>SER_JP_MDR_PSEUDOMONAS_AERUGINOSA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV49" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA49" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB49" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC49" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9903,7 +10302,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -9986,7 +10385,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10">
@@ -9996,7 +10395,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11">
@@ -10016,7 +10415,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13">
@@ -10048,7 +10447,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>120</v>
+        <v>126</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d229/2026-2029.xlsx
+++ b/diseases/d229/2026-2029.xlsx
@@ -10269,6 +10269,405 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>D229</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>multidrug-resistant-pseudomonas-aeruginosa-infection</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Multidrug-resistant Pseudomonas aeruginosa infection</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>D229</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Multidrug-resistant Pseudomonas aeruginosa infection</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>多重耐药铜绿假单胞菌感染</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>3</v>
+      </c>
+      <c r="O50" t="n">
+        <v>3</v>
+      </c>
+      <c r="P50" t="n">
+        <v>3</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0.002450425222697299</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>SER_JP_MDR_PSEUDOMONAS_AERUGINOSA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP50" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ50" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS50" t="inlineStr">
+        <is>
+          <t>SER_JP_MDR_PSEUDOMONAS_AERUGINOSA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV50" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA50" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB50" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC50" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>D229</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>multidrug-resistant-pseudomonas-aeruginosa-infection</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Multidrug-resistant Pseudomonas aeruginosa infection</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>D229</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Multidrug-resistant Pseudomonas aeruginosa infection</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>多重耐药铜绿假单胞菌感染</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>3</v>
+      </c>
+      <c r="O51" t="n">
+        <v>3</v>
+      </c>
+      <c r="P51" t="n">
+        <v>3</v>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>SER_JP_MDR_PSEUDOMONAS_AERUGINOSA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>SER_JP_MDR_PSEUDOMONAS_AERUGINOSA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Multidrug-resistant Pseudomonas aeruginosa infection</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG51" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Japan NIID multidrug-resistant Pseudomonas aeruginosa infection notifications.</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN51" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP51" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ51" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS51" t="inlineStr">
+        <is>
+          <t>SER_JP_MDR_PSEUDOMONAS_AERUGINOSA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV51" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA51" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB51" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC51" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10302,7 +10701,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -10385,7 +10784,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10">
@@ -10395,7 +10794,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11">
@@ -10415,7 +10814,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13">
@@ -10447,7 +10846,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d229/2026-2029.xlsx
+++ b/diseases/d229/2026-2029.xlsx
@@ -10668,6 +10668,405 @@
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>D229</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>multidrug-resistant-pseudomonas-aeruginosa-infection</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Multidrug-resistant Pseudomonas aeruginosa infection</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>D229</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Multidrug-resistant Pseudomonas aeruginosa infection</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>多重耐药铜绿假单胞菌感染</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>7</v>
+      </c>
+      <c r="O52" t="n">
+        <v>7</v>
+      </c>
+      <c r="P52" t="n">
+        <v>7</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0.005717658852960364</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>SER_JP_MDR_PSEUDOMONAS_AERUGINOSA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP52" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ52" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS52" t="inlineStr">
+        <is>
+          <t>SER_JP_MDR_PSEUDOMONAS_AERUGINOSA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV52" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA52" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB52" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC52" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>D229</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>multidrug-resistant-pseudomonas-aeruginosa-infection</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Multidrug-resistant Pseudomonas aeruginosa infection</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>D229</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Multidrug-resistant Pseudomonas aeruginosa infection</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>多重耐药铜绿假单胞菌感染</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>7</v>
+      </c>
+      <c r="O53" t="n">
+        <v>7</v>
+      </c>
+      <c r="P53" t="n">
+        <v>7</v>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>SER_JP_MDR_PSEUDOMONAS_AERUGINOSA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>SER_JP_MDR_PSEUDOMONAS_AERUGINOSA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>Multidrug-resistant Pseudomonas aeruginosa infection</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD53" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG53" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Japan NIID multidrug-resistant Pseudomonas aeruginosa infection notifications.</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN53" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP53" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ53" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS53" t="inlineStr">
+        <is>
+          <t>SER_JP_MDR_PSEUDOMONAS_AERUGINOSA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV53" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA53" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB53" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC53" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10701,7 +11100,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -10784,7 +11183,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10">
@@ -10794,7 +11193,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11">
@@ -10814,7 +11213,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13">
@@ -10846,7 +11245,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>129</v>
+        <v>136</v>
       </c>
     </row>
     <row r="16">
